--- a/dcf/UBER.xlsx
+++ b/dcf/UBER.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1151,25 +1151,25 @@
         <v>12</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>127.2893231452607</v>
+        <v>113.8415394589158</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>122.2511356439474</v>
+        <v>109.3728272105222</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>117.4469135823104</v>
+        <v>105.1108998612044</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>112.86451228296</v>
+        <v>101.0450411084451</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>108.492476104254</v>
+        <v>97.16514211561589</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>104.3199962216964</v>
+        <v>93.46166431051921</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>100.3368711807588</v>
+        <v>89.92560462520368</v>
       </c>
     </row>
     <row r="6">
@@ -1177,25 +1177,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>134.2113142486149</v>
+        <v>119.9329575923575</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>128.8595803982822</v>
+        <v>115.1883215689151</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>123.7573643274338</v>
+        <v>110.6641566517842</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>118.8916836021947</v>
+        <v>106.3490093047571</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>114.2502934932012</v>
+        <v>102.232076286491</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>109.8216417257304</v>
+        <v>98.30316478150374</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>105.594826202636</v>
+        <v>94.55265514966375</v>
       </c>
     </row>
     <row r="7">
@@ -1203,25 +1203,25 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>141.1333053519692</v>
+        <v>126.0243757257992</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>135.4680251526169</v>
+        <v>121.003815927308</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>130.0678150725572</v>
+        <v>116.2174134423641</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>124.9188549214294</v>
+        <v>111.6529775010691</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>120.0081108821484</v>
+        <v>107.2990104573661</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>115.3232872297643</v>
+        <v>103.1446652524883</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>110.8527812245131</v>
+        <v>99.17970567412384</v>
       </c>
     </row>
     <row r="8">
@@ -1229,25 +1229,25 @@
         <v>15</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>148.0552964553234</v>
+        <v>132.1157938592409</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>142.0764699069517</v>
+        <v>126.8193102857009</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>136.3782658176806</v>
+        <v>121.770670232944</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>130.946026240664</v>
+        <v>116.9569456973812</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>125.7659282710956</v>
+        <v>112.3659446282412</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>120.8249327337983</v>
+        <v>107.9861657234728</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>116.1107362463902</v>
+        <v>103.8067561985839</v>
       </c>
     </row>
     <row r="9">
@@ -1255,25 +1255,25 @@
         <v>16</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>154.9772875586776</v>
+        <v>138.2072119926826</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>148.6849146612864</v>
+        <v>132.6348046440938</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>142.688716562804</v>
+        <v>127.3239270235238</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>136.9731975598987</v>
+        <v>122.2609138936932</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>131.5237456600428</v>
+        <v>117.4328787991162</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>126.3265782378322</v>
+        <v>112.8276661944574</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>121.3686912682674</v>
+        <v>108.433806723044</v>
       </c>
     </row>
     <row r="10">
@@ -1281,25 +1281,25 @@
         <v>17</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>161.8992786620319</v>
+        <v>144.2986301261243</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>155.2933594156212</v>
+        <v>138.4502990024867</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>148.9991673079274</v>
+        <v>132.8771838141037</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>143.0003688791333</v>
+        <v>127.5648820900052</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>137.28156304899</v>
+        <v>122.4998129699913</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>131.8282237418662</v>
+        <v>117.6691666654419</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>126.6266462901445</v>
+        <v>113.060857247504</v>
       </c>
     </row>
     <row r="11">
@@ -1307,25 +1307,25 @@
         <v>18</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>168.8212697653861</v>
+        <v>150.390048259566</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>161.9018041699559</v>
+        <v>144.2657933608796</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>155.3096180530508</v>
+        <v>138.4304406046836</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>149.0275401983679</v>
+        <v>132.8688502863172</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>143.0393804379372</v>
+        <v>127.5667471408664</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>137.3298692459001</v>
+        <v>122.5106671364265</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>131.8846013120216</v>
+        <v>117.6879077719641</v>
       </c>
     </row>
     <row r="13">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9825500254636282</v>
+        <v>0.984930808930343</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24472,7 +24472,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24624,13 +24624,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>130.946026240664</v>
+        <v>116.9569456973812</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>182.5013231096266</v>
+        <v>159.6601494374809</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>92.41216523306376</v>
+        <v>84.28891013602654</v>
       </c>
     </row>
     <row r="59">
